--- a/이벤트 스캐쥴.xlsx
+++ b/이벤트 스캐쥴.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fathermade\Desktop\스케쥴\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF27EEA-FE9D-4C09-80FF-9208FA060092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C38D0FF-3A39-4E50-BB4A-473DE1D83794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{960D76DD-7980-44EA-8846-33B5604DDBBF}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{960D76DD-7980-44EA-8846-33B5604DDBBF}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="2" r:id="rId1"/>
@@ -1590,7 +1590,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1691,6 +1691,9 @@
     <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1725,6 +1728,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2128,10 +2134,10 @@
       <c r="F3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="37" t="s">
         <v>74</v>
       </c>
       <c r="J3" s="19" t="s">
@@ -2166,10 +2172,10 @@
       <c r="F4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="37" t="s">
         <v>75</v>
       </c>
       <c r="J4" s="19" t="s">
@@ -2195,10 +2201,10 @@
       <c r="F5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="37" t="s">
         <v>76</v>
       </c>
       <c r="J5" s="19" t="s">
@@ -2224,10 +2230,10 @@
       <c r="F6" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="36" t="s">
+      <c r="H6" s="37" t="s">
         <v>77</v>
       </c>
       <c r="J6" s="19" t="s">
@@ -2568,7 +2574,7 @@
       <c r="H19" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="J19" s="35" t="s">
+      <c r="J19" s="36" t="s">
         <v>221</v>
       </c>
       <c r="K19" s="32" t="s">
@@ -2606,7 +2612,7 @@
       <c r="H20" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J20" s="35" t="s">
+      <c r="J20" s="36" t="s">
         <v>222</v>
       </c>
       <c r="K20" s="32" t="s">
@@ -2644,7 +2650,7 @@
       <c r="H21" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="J21" s="35" t="s">
+      <c r="J21" s="36" t="s">
         <v>223</v>
       </c>
       <c r="K21" s="32" t="s">
@@ -2682,7 +2688,7 @@
       <c r="H22" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="J22" s="35" t="s">
+      <c r="J22" s="36" t="s">
         <v>224</v>
       </c>
       <c r="K22" s="32" t="s">
@@ -2746,7 +2752,7 @@
       <c r="H24" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="J24" s="35" t="s">
+      <c r="J24" s="36" t="s">
         <v>345</v>
       </c>
       <c r="K24" s="32" t="s">
@@ -2778,7 +2784,7 @@
       <c r="H25" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="J25" s="35" t="s">
+      <c r="J25" s="36" t="s">
         <v>362</v>
       </c>
       <c r="K25" s="32" t="s">
@@ -2810,7 +2816,7 @@
       <c r="H26" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="J26" s="35" t="s">
+      <c r="J26" s="36" t="s">
         <v>365</v>
       </c>
       <c r="K26" s="32" t="s">
@@ -2836,7 +2842,7 @@
       <c r="H27" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="J27" s="35"/>
+      <c r="J27" s="36"/>
       <c r="K27" s="32"/>
       <c r="L27" s="32"/>
       <c r="N27" s="19"/>
@@ -2856,7 +2862,7 @@
       <c r="H28" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="35"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="32"/>
       <c r="L28" s="32"/>
       <c r="N28" s="19"/>
@@ -2876,7 +2882,7 @@
       <c r="H29" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="J29" s="35"/>
+      <c r="J29" s="36"/>
       <c r="K29" s="32"/>
       <c r="L29" s="32"/>
       <c r="N29" s="19"/>
@@ -2896,7 +2902,7 @@
       <c r="H30" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="J30" s="35"/>
+      <c r="J30" s="36"/>
       <c r="K30" s="32"/>
       <c r="L30" s="32"/>
       <c r="N30" s="19"/>
@@ -2916,7 +2922,7 @@
       <c r="H31" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="J31" s="35"/>
+      <c r="J31" s="36"/>
       <c r="K31" s="32"/>
       <c r="L31" s="32"/>
       <c r="N31" s="19"/>
@@ -2944,7 +2950,7 @@
       <c r="T32" s="21"/>
     </row>
     <row r="33" spans="6:20" x14ac:dyDescent="0.45">
-      <c r="F33" s="35" t="s">
+      <c r="F33" s="36" t="s">
         <v>60</v>
       </c>
       <c r="G33" s="17" t="s">
@@ -2970,7 +2976,7 @@
       <c r="T33" s="21"/>
     </row>
     <row r="34" spans="6:20" x14ac:dyDescent="0.45">
-      <c r="F34" s="35" t="s">
+      <c r="F34" s="36" t="s">
         <v>61</v>
       </c>
       <c r="G34" s="17" t="s">
@@ -2996,7 +3002,7 @@
       <c r="T34" s="21"/>
     </row>
     <row r="35" spans="6:20" x14ac:dyDescent="0.45">
-      <c r="F35" s="35" t="s">
+      <c r="F35" s="36" t="s">
         <v>62</v>
       </c>
       <c r="G35" s="17" t="s">
@@ -3347,7 +3353,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="49" spans="4:16" x14ac:dyDescent="0.45">
+    <row r="49" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F49" s="16" t="s">
         <v>305</v>
       </c>
@@ -3366,17 +3372,17 @@
       <c r="L49" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="N49" s="28" t="s">
+      <c r="N49" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="O49" s="30" t="s">
+      <c r="O49" s="35" t="s">
         <v>227</v>
       </c>
-      <c r="P49" s="30" t="s">
+      <c r="P49" s="35" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="4:16" x14ac:dyDescent="0.45">
+    <row r="50" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F50" s="16" t="s">
         <v>306</v>
       </c>
@@ -3395,17 +3401,20 @@
       <c r="L50" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="N50" s="28" t="s">
+      <c r="N50" s="34" t="s">
         <v>331</v>
       </c>
-      <c r="O50" s="30" t="s">
+      <c r="O50" s="35" t="s">
         <v>333</v>
       </c>
-      <c r="P50" s="30" t="s">
+      <c r="P50" s="35" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="51" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="Q50" s="47"/>
+      <c r="R50" s="47"/>
+      <c r="S50" s="47"/>
+    </row>
+    <row r="51" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F51" s="16" t="s">
         <v>307</v>
       </c>
@@ -3427,14 +3436,17 @@
       <c r="N51" s="28" t="s">
         <v>379</v>
       </c>
-      <c r="O51" s="34" t="s">
+      <c r="O51" s="35" t="s">
         <v>226</v>
       </c>
-      <c r="P51" s="34" t="s">
+      <c r="P51" s="35" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="52" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="Q51" s="47"/>
+      <c r="R51" s="47"/>
+      <c r="S51" s="47"/>
+    </row>
+    <row r="52" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F52" s="16" t="s">
         <v>308</v>
       </c>
@@ -3456,14 +3468,17 @@
       <c r="N52" s="28" t="s">
         <v>380</v>
       </c>
-      <c r="O52" s="34" t="s">
+      <c r="O52" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="P52" s="34" t="s">
+      <c r="P52" s="35" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="53" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="Q52" s="47"/>
+      <c r="R52" s="47"/>
+      <c r="S52" s="47"/>
+    </row>
+    <row r="53" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F53" s="16" t="s">
         <v>309</v>
       </c>
@@ -3485,14 +3500,17 @@
       <c r="N53" s="28" t="s">
         <v>383</v>
       </c>
-      <c r="O53" s="34" t="s">
+      <c r="O53" s="35" t="s">
         <v>381</v>
       </c>
-      <c r="P53" s="34" t="s">
+      <c r="P53" s="35" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="54" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="Q53" s="47"/>
+      <c r="R53" s="47"/>
+      <c r="S53" s="47"/>
+    </row>
+    <row r="54" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F54" s="16" t="s">
         <v>310</v>
       </c>
@@ -3514,14 +3532,17 @@
       <c r="N54" s="28" t="s">
         <v>384</v>
       </c>
-      <c r="O54" s="34" t="s">
+      <c r="O54" s="35" t="s">
         <v>231</v>
       </c>
-      <c r="P54" s="34" t="s">
+      <c r="P54" s="35" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="55" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="Q54" s="47"/>
+      <c r="R54" s="47"/>
+      <c r="S54" s="47"/>
+    </row>
+    <row r="55" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F55" s="16" t="s">
         <v>311</v>
       </c>
@@ -3543,14 +3564,17 @@
       <c r="N55" s="28" t="s">
         <v>385</v>
       </c>
-      <c r="O55" s="38" t="s">
+      <c r="O55" s="39" t="s">
         <v>342</v>
       </c>
-      <c r="P55" s="38" t="s">
+      <c r="P55" s="39" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="56" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="Q55" s="47"/>
+      <c r="R55" s="47"/>
+      <c r="S55" s="47"/>
+    </row>
+    <row r="56" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F56" s="16" t="s">
         <v>321</v>
       </c>
@@ -3572,14 +3596,17 @@
       <c r="N56" s="28" t="s">
         <v>386</v>
       </c>
-      <c r="O56" s="38" t="s">
+      <c r="O56" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="P56" s="38" t="s">
+      <c r="P56" s="39" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="57" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="Q56" s="47"/>
+      <c r="R56" s="47"/>
+      <c r="S56" s="47"/>
+    </row>
+    <row r="57" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F57" s="16" t="s">
         <v>348</v>
       </c>
@@ -3601,14 +3628,17 @@
       <c r="N57" s="28" t="s">
         <v>387</v>
       </c>
-      <c r="O57" s="38" t="s">
+      <c r="O57" s="39" t="s">
         <v>363</v>
       </c>
-      <c r="P57" s="38" t="s">
+      <c r="P57" s="39" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="58" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="Q57" s="47"/>
+      <c r="R57" s="47"/>
+      <c r="S57" s="47"/>
+    </row>
+    <row r="58" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F58" s="16" t="s">
         <v>347</v>
       </c>
@@ -3628,7 +3658,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="4:16" x14ac:dyDescent="0.45">
+    <row r="59" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F59" s="16" t="s">
         <v>344</v>
       </c>
@@ -3648,7 +3678,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="4:16" x14ac:dyDescent="0.45">
+    <row r="60" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F60" s="16" t="s">
         <v>372</v>
       </c>
@@ -3668,7 +3698,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="61" spans="4:16" x14ac:dyDescent="0.45">
+    <row r="61" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F61" s="16" t="s">
         <v>373</v>
       </c>
@@ -3688,7 +3718,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="62" spans="4:16" x14ac:dyDescent="0.45">
+    <row r="62" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F62" s="16" t="s">
         <v>375</v>
       </c>
@@ -3708,7 +3738,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="63" spans="4:16" x14ac:dyDescent="0.45">
+    <row r="63" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F63" s="16" t="s">
         <v>376</v>
       </c>
@@ -3728,7 +3758,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="64" spans="4:16" x14ac:dyDescent="0.45">
+    <row r="64" spans="4:19" x14ac:dyDescent="0.45">
       <c r="D64" s="6"/>
       <c r="F64" s="16" t="s">
         <v>343</v>
@@ -3804,7 +3834,7 @@
       <c r="L68" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="R68" s="37" t="s">
+      <c r="R68" s="38" t="s">
         <v>63</v>
       </c>
       <c r="S68" s="31" t="s">
@@ -3824,7 +3854,7 @@
       <c r="L69" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="R69" s="37" t="s">
+      <c r="R69" s="38" t="s">
         <v>64</v>
       </c>
       <c r="S69" s="31" t="s">
@@ -3844,7 +3874,7 @@
       <c r="L70" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="R70" s="37" t="s">
+      <c r="R70" s="38" t="s">
         <v>65</v>
       </c>
       <c r="S70" s="31" t="s">
@@ -3864,7 +3894,7 @@
       <c r="L71" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="R71" s="37" t="s">
+      <c r="R71" s="38" t="s">
         <v>66</v>
       </c>
       <c r="S71" s="31" t="s">
@@ -3884,7 +3914,7 @@
       <c r="L72" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="R72" s="37" t="s">
+      <c r="R72" s="38" t="s">
         <v>67</v>
       </c>
       <c r="S72" s="31" t="s">
@@ -3904,7 +3934,7 @@
       <c r="L73" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="R73" s="37" t="s">
+      <c r="R73" s="38" t="s">
         <v>68</v>
       </c>
       <c r="S73" s="31" t="s">
@@ -3924,7 +3954,7 @@
       <c r="L74" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="R74" s="37" t="s">
+      <c r="R74" s="38" t="s">
         <v>69</v>
       </c>
       <c r="S74" s="31" t="s">
@@ -3944,7 +3974,7 @@
       <c r="L75" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="R75" s="37" t="s">
+      <c r="R75" s="38" t="s">
         <v>70</v>
       </c>
       <c r="S75" s="31" t="s">
@@ -3964,7 +3994,7 @@
       <c r="L76" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="R76" s="37" t="s">
+      <c r="R76" s="38" t="s">
         <v>71</v>
       </c>
       <c r="S76" s="31" t="s">
@@ -4020,7 +4050,7 @@
       </c>
     </row>
     <row r="80" spans="3:20" x14ac:dyDescent="0.45">
-      <c r="C80" s="35" t="s">
+      <c r="C80" s="36" t="s">
         <v>239</v>
       </c>
       <c r="D80" s="17" t="s">
@@ -4029,7 +4059,7 @@
       <c r="E80" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F80" s="35" t="s">
+      <c r="F80" s="36" t="s">
         <v>351</v>
       </c>
       <c r="J80" s="28" t="s">
@@ -4043,7 +4073,7 @@
       </c>
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.45">
-      <c r="C81" s="35" t="s">
+      <c r="C81" s="36" t="s">
         <v>240</v>
       </c>
       <c r="D81" s="17" t="s">
@@ -4052,7 +4082,7 @@
       <c r="E81" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F81" s="35" t="s">
+      <c r="F81" s="36" t="s">
         <v>353</v>
       </c>
       <c r="J81" s="28" t="s">
@@ -4066,7 +4096,7 @@
       </c>
     </row>
     <row r="82" spans="3:12" x14ac:dyDescent="0.45">
-      <c r="C82" s="35" t="s">
+      <c r="C82" s="36" t="s">
         <v>241</v>
       </c>
       <c r="D82" s="17" t="s">
@@ -4075,7 +4105,7 @@
       <c r="E82" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F82" s="35" t="s">
+      <c r="F82" s="36" t="s">
         <v>354</v>
       </c>
       <c r="J82" s="28" t="s">
@@ -4089,7 +4119,7 @@
       </c>
     </row>
     <row r="83" spans="3:12" x14ac:dyDescent="0.45">
-      <c r="C83" s="35" t="s">
+      <c r="C83" s="36" t="s">
         <v>350</v>
       </c>
       <c r="D83" s="17" t="s">
@@ -4098,7 +4128,7 @@
       <c r="E83" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F83" s="35" t="s">
+      <c r="F83" s="36" t="s">
         <v>355</v>
       </c>
       <c r="J83" s="28" t="s">
@@ -4263,124 +4293,124 @@
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="44"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="43" t="s">
+      <c r="C6" s="45"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="42" t="s">
+      <c r="F6" s="45"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42" t="s">
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B7" s="39" t="s">
+      <c r="B7" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="39" t="s">
+      <c r="C7" s="41"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="40"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="39" t="s">
+      <c r="F7" s="41"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="40"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="39" t="s">
+      <c r="I7" s="41"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="41"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="41"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="42"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="39" t="s">
+      <c r="C8" s="41"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="39">
+      <c r="F8" s="41"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="40">
         <v>3</v>
       </c>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
-      <c r="K8" s="39" t="s">
+      <c r="I8" s="41"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="42"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="39" t="s">
+      <c r="C9" s="41"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="39">
+      <c r="F9" s="41"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="40">
         <v>3</v>
       </c>
-      <c r="I9" s="40"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="39" t="s">
+      <c r="I9" s="41"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="42"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="39" t="s">
+      <c r="C10" s="41"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="39">
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="40">
         <v>3</v>
       </c>
-      <c r="I10" s="40"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="39" t="s">
+      <c r="I10" s="41"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="42"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B13" s="1" t="s">
@@ -4388,76 +4418,76 @@
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="43" t="s">
+      <c r="C14" s="45"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="44"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="42" t="s">
+      <c r="F14" s="45"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42" t="s">
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42"/>
+      <c r="L14" s="43"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="O14" s="43"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="39" t="s">
+      <c r="C15" s="41"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="39" t="s">
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="40"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="39" t="s">
+      <c r="I15" s="41"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="42"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="39" t="s">
+      <c r="C16" s="41"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="39" t="s">
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="I16" s="40"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="39" t="s">
+      <c r="I16" s="41"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="42"/>
     </row>
     <row r="22" spans="3:24" x14ac:dyDescent="0.45">
       <c r="F22" s="4" t="s">
@@ -4488,11 +4518,11 @@
         <v>32</v>
       </c>
       <c r="N23" s="5"/>
-      <c r="P23" s="39" t="s">
+      <c r="P23" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="Q23" s="40"/>
-      <c r="R23" s="41"/>
+      <c r="Q23" s="41"/>
+      <c r="R23" s="42"/>
       <c r="S23" s="9" t="s">
         <v>73</v>
       </c>
@@ -4511,11 +4541,11 @@
         <v>75</v>
       </c>
       <c r="N24" s="5"/>
-      <c r="P24" s="39" t="s">
+      <c r="P24" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="Q24" s="40"/>
-      <c r="R24" s="41"/>
+      <c r="Q24" s="41"/>
+      <c r="R24" s="42"/>
       <c r="S24" s="8" t="s">
         <v>108</v>
       </c>
@@ -4537,11 +4567,11 @@
         <v>76</v>
       </c>
       <c r="N25" s="5"/>
-      <c r="P25" s="39" t="s">
+      <c r="P25" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="Q25" s="40"/>
-      <c r="R25" s="41"/>
+      <c r="Q25" s="41"/>
+      <c r="R25" s="42"/>
       <c r="S25" s="8" t="s">
         <v>111</v>
       </c>
@@ -4563,11 +4593,11 @@
         <v>77</v>
       </c>
       <c r="N26" s="5"/>
-      <c r="P26" s="39" t="s">
+      <c r="P26" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="Q26" s="40"/>
-      <c r="R26" s="41"/>
+      <c r="Q26" s="41"/>
+      <c r="R26" s="42"/>
       <c r="S26" s="8" t="s">
         <v>113</v>
       </c>

--- a/이벤트 스캐쥴.xlsx
+++ b/이벤트 스캐쥴.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fathermade\Desktop\스케쥴\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C38D0FF-3A39-4E50-BB4A-473DE1D83794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2278F629-0DD8-4C2F-B9BF-2040F4FB9744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{960D76DD-7980-44EA-8846-33B5604DDBBF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{960D76DD-7980-44EA-8846-33B5604DDBBF}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="390">
   <si>
     <t>※ 패키지 상품 판매 주기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1404,6 +1404,12 @@
   </si>
   <si>
     <t>특별 보상!13</t>
+  </si>
+  <si>
+    <t>특별 보상!14</t>
+  </si>
+  <si>
+    <t>특별 보상!15</t>
   </si>
 </sst>
 </file>
@@ -1590,7 +1596,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1691,9 +1697,6 @@
     <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1709,16 +1712,7 @@
     <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1730,7 +1724,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2134,10 +2137,10 @@
       <c r="F3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="36" t="s">
         <v>74</v>
       </c>
       <c r="J3" s="19" t="s">
@@ -2172,10 +2175,10 @@
       <c r="F4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="37" t="s">
+      <c r="G4" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="36" t="s">
         <v>75</v>
       </c>
       <c r="J4" s="19" t="s">
@@ -2201,10 +2204,10 @@
       <c r="F5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="H5" s="37" t="s">
+      <c r="H5" s="36" t="s">
         <v>76</v>
       </c>
       <c r="J5" s="19" t="s">
@@ -2230,10 +2233,10 @@
       <c r="F6" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="36" t="s">
         <v>77</v>
       </c>
       <c r="J6" s="19" t="s">
@@ -2574,7 +2577,7 @@
       <c r="H19" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="J19" s="36" t="s">
+      <c r="J19" s="35" t="s">
         <v>221</v>
       </c>
       <c r="K19" s="32" t="s">
@@ -2612,7 +2615,7 @@
       <c r="H20" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J20" s="36" t="s">
+      <c r="J20" s="35" t="s">
         <v>222</v>
       </c>
       <c r="K20" s="32" t="s">
@@ -2650,7 +2653,7 @@
       <c r="H21" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="J21" s="36" t="s">
+      <c r="J21" s="35" t="s">
         <v>223</v>
       </c>
       <c r="K21" s="32" t="s">
@@ -2688,7 +2691,7 @@
       <c r="H22" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="J22" s="36" t="s">
+      <c r="J22" s="35" t="s">
         <v>224</v>
       </c>
       <c r="K22" s="32" t="s">
@@ -2752,7 +2755,7 @@
       <c r="H24" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="J24" s="36" t="s">
+      <c r="J24" s="35" t="s">
         <v>345</v>
       </c>
       <c r="K24" s="32" t="s">
@@ -2784,7 +2787,7 @@
       <c r="H25" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="J25" s="36" t="s">
+      <c r="J25" s="35" t="s">
         <v>362</v>
       </c>
       <c r="K25" s="32" t="s">
@@ -2816,7 +2819,7 @@
       <c r="H26" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="J26" s="36" t="s">
+      <c r="J26" s="35" t="s">
         <v>365</v>
       </c>
       <c r="K26" s="32" t="s">
@@ -2842,7 +2845,7 @@
       <c r="H27" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="J27" s="36"/>
+      <c r="J27" s="35"/>
       <c r="K27" s="32"/>
       <c r="L27" s="32"/>
       <c r="N27" s="19"/>
@@ -2862,7 +2865,7 @@
       <c r="H28" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="36"/>
+      <c r="J28" s="35"/>
       <c r="K28" s="32"/>
       <c r="L28" s="32"/>
       <c r="N28" s="19"/>
@@ -2882,7 +2885,7 @@
       <c r="H29" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="J29" s="36"/>
+      <c r="J29" s="35"/>
       <c r="K29" s="32"/>
       <c r="L29" s="32"/>
       <c r="N29" s="19"/>
@@ -2902,7 +2905,7 @@
       <c r="H30" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="J30" s="36"/>
+      <c r="J30" s="35"/>
       <c r="K30" s="32"/>
       <c r="L30" s="32"/>
       <c r="N30" s="19"/>
@@ -2922,7 +2925,7 @@
       <c r="H31" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="J31" s="36"/>
+      <c r="J31" s="35"/>
       <c r="K31" s="32"/>
       <c r="L31" s="32"/>
       <c r="N31" s="19"/>
@@ -2950,7 +2953,7 @@
       <c r="T32" s="21"/>
     </row>
     <row r="33" spans="6:20" x14ac:dyDescent="0.45">
-      <c r="F33" s="36" t="s">
+      <c r="F33" s="35" t="s">
         <v>60</v>
       </c>
       <c r="G33" s="17" t="s">
@@ -2976,7 +2979,7 @@
       <c r="T33" s="21"/>
     </row>
     <row r="34" spans="6:20" x14ac:dyDescent="0.45">
-      <c r="F34" s="36" t="s">
+      <c r="F34" s="35" t="s">
         <v>61</v>
       </c>
       <c r="G34" s="17" t="s">
@@ -3002,7 +3005,7 @@
       <c r="T34" s="21"/>
     </row>
     <row r="35" spans="6:20" x14ac:dyDescent="0.45">
-      <c r="F35" s="36" t="s">
+      <c r="F35" s="35" t="s">
         <v>62</v>
       </c>
       <c r="G35" s="17" t="s">
@@ -3372,13 +3375,13 @@
       <c r="L49" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="N49" s="34" t="s">
-        <v>330</v>
-      </c>
-      <c r="O49" s="35" t="s">
+      <c r="N49" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="O49" s="34" t="s">
         <v>227</v>
       </c>
-      <c r="P49" s="35" t="s">
+      <c r="P49" s="34" t="s">
         <v>227</v>
       </c>
     </row>
@@ -3401,18 +3404,18 @@
       <c r="L50" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="N50" s="34" t="s">
-        <v>331</v>
-      </c>
-      <c r="O50" s="35" t="s">
+      <c r="N50" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="O50" s="34" t="s">
         <v>333</v>
       </c>
-      <c r="P50" s="35" t="s">
+      <c r="P50" s="34" t="s">
         <v>333</v>
       </c>
-      <c r="Q50" s="47"/>
-      <c r="R50" s="47"/>
-      <c r="S50" s="47"/>
+      <c r="Q50" s="39"/>
+      <c r="R50" s="39"/>
+      <c r="S50" s="39"/>
     </row>
     <row r="51" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F51" s="16" t="s">
@@ -3434,17 +3437,17 @@
         <v>81</v>
       </c>
       <c r="N51" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="O51" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="O51" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="P51" s="35" t="s">
+      <c r="P51" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="Q51" s="47"/>
-      <c r="R51" s="47"/>
-      <c r="S51" s="47"/>
+      <c r="Q51" s="39"/>
+      <c r="R51" s="39"/>
+      <c r="S51" s="39"/>
     </row>
     <row r="52" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F52" s="16" t="s">
@@ -3466,17 +3469,17 @@
         <v>195</v>
       </c>
       <c r="N52" s="28" t="s">
-        <v>380</v>
-      </c>
-      <c r="O52" s="35" t="s">
+        <v>384</v>
+      </c>
+      <c r="O52" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="P52" s="35" t="s">
+      <c r="P52" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="Q52" s="47"/>
-      <c r="R52" s="47"/>
-      <c r="S52" s="47"/>
+      <c r="Q52" s="39"/>
+      <c r="R52" s="39"/>
+      <c r="S52" s="39"/>
     </row>
     <row r="53" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F53" s="16" t="s">
@@ -3498,17 +3501,17 @@
         <v>82</v>
       </c>
       <c r="N53" s="28" t="s">
-        <v>383</v>
-      </c>
-      <c r="O53" s="35" t="s">
+        <v>385</v>
+      </c>
+      <c r="O53" s="34" t="s">
         <v>381</v>
       </c>
-      <c r="P53" s="35" t="s">
+      <c r="P53" s="34" t="s">
         <v>381</v>
       </c>
-      <c r="Q53" s="47"/>
-      <c r="R53" s="47"/>
-      <c r="S53" s="47"/>
+      <c r="Q53" s="39"/>
+      <c r="R53" s="39"/>
+      <c r="S53" s="39"/>
     </row>
     <row r="54" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F54" s="16" t="s">
@@ -3530,17 +3533,17 @@
         <v>83</v>
       </c>
       <c r="N54" s="28" t="s">
-        <v>384</v>
-      </c>
-      <c r="O54" s="35" t="s">
+        <v>386</v>
+      </c>
+      <c r="O54" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="P54" s="35" t="s">
+      <c r="P54" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="Q54" s="47"/>
-      <c r="R54" s="47"/>
-      <c r="S54" s="47"/>
+      <c r="Q54" s="39"/>
+      <c r="R54" s="39"/>
+      <c r="S54" s="39"/>
     </row>
     <row r="55" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F55" s="16" t="s">
@@ -3562,17 +3565,17 @@
         <v>131</v>
       </c>
       <c r="N55" s="28" t="s">
-        <v>385</v>
-      </c>
-      <c r="O55" s="39" t="s">
+        <v>387</v>
+      </c>
+      <c r="O55" s="38" t="s">
         <v>342</v>
       </c>
-      <c r="P55" s="39" t="s">
+      <c r="P55" s="38" t="s">
         <v>342</v>
       </c>
-      <c r="Q55" s="47"/>
-      <c r="R55" s="47"/>
-      <c r="S55" s="47"/>
+      <c r="Q55" s="39"/>
+      <c r="R55" s="39"/>
+      <c r="S55" s="39"/>
     </row>
     <row r="56" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F56" s="16" t="s">
@@ -3594,17 +3597,17 @@
         <v>278</v>
       </c>
       <c r="N56" s="28" t="s">
-        <v>386</v>
-      </c>
-      <c r="O56" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="O56" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="P56" s="39" t="s">
+      <c r="P56" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="Q56" s="47"/>
-      <c r="R56" s="47"/>
-      <c r="S56" s="47"/>
+      <c r="Q56" s="39"/>
+      <c r="R56" s="39"/>
+      <c r="S56" s="39"/>
     </row>
     <row r="57" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F57" s="16" t="s">
@@ -3626,17 +3629,17 @@
         <v>145</v>
       </c>
       <c r="N57" s="28" t="s">
-        <v>387</v>
-      </c>
-      <c r="O57" s="39" t="s">
+        <v>389</v>
+      </c>
+      <c r="O57" s="38" t="s">
         <v>363</v>
       </c>
-      <c r="P57" s="39" t="s">
+      <c r="P57" s="38" t="s">
         <v>363</v>
       </c>
-      <c r="Q57" s="47"/>
-      <c r="R57" s="47"/>
-      <c r="S57" s="47"/>
+      <c r="Q57" s="39"/>
+      <c r="R57" s="39"/>
+      <c r="S57" s="39"/>
     </row>
     <row r="58" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F58" s="16" t="s">
@@ -3834,7 +3837,7 @@
       <c r="L68" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="R68" s="38" t="s">
+      <c r="R68" s="37" t="s">
         <v>63</v>
       </c>
       <c r="S68" s="31" t="s">
@@ -3854,7 +3857,7 @@
       <c r="L69" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="R69" s="38" t="s">
+      <c r="R69" s="37" t="s">
         <v>64</v>
       </c>
       <c r="S69" s="31" t="s">
@@ -3874,7 +3877,7 @@
       <c r="L70" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="R70" s="38" t="s">
+      <c r="R70" s="37" t="s">
         <v>65</v>
       </c>
       <c r="S70" s="31" t="s">
@@ -3894,7 +3897,7 @@
       <c r="L71" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="R71" s="38" t="s">
+      <c r="R71" s="37" t="s">
         <v>66</v>
       </c>
       <c r="S71" s="31" t="s">
@@ -3914,7 +3917,7 @@
       <c r="L72" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="R72" s="38" t="s">
+      <c r="R72" s="37" t="s">
         <v>67</v>
       </c>
       <c r="S72" s="31" t="s">
@@ -3934,7 +3937,7 @@
       <c r="L73" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="R73" s="38" t="s">
+      <c r="R73" s="37" t="s">
         <v>68</v>
       </c>
       <c r="S73" s="31" t="s">
@@ -3954,7 +3957,7 @@
       <c r="L74" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="R74" s="38" t="s">
+      <c r="R74" s="37" t="s">
         <v>69</v>
       </c>
       <c r="S74" s="31" t="s">
@@ -3974,7 +3977,7 @@
       <c r="L75" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="R75" s="38" t="s">
+      <c r="R75" s="37" t="s">
         <v>70</v>
       </c>
       <c r="S75" s="31" t="s">
@@ -3994,7 +3997,7 @@
       <c r="L76" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="R76" s="38" t="s">
+      <c r="R76" s="37" t="s">
         <v>71</v>
       </c>
       <c r="S76" s="31" t="s">
@@ -4050,7 +4053,7 @@
       </c>
     </row>
     <row r="80" spans="3:20" x14ac:dyDescent="0.45">
-      <c r="C80" s="36" t="s">
+      <c r="C80" s="35" t="s">
         <v>239</v>
       </c>
       <c r="D80" s="17" t="s">
@@ -4059,7 +4062,7 @@
       <c r="E80" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F80" s="36" t="s">
+      <c r="F80" s="35" t="s">
         <v>351</v>
       </c>
       <c r="J80" s="28" t="s">
@@ -4073,7 +4076,7 @@
       </c>
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.45">
-      <c r="C81" s="36" t="s">
+      <c r="C81" s="35" t="s">
         <v>240</v>
       </c>
       <c r="D81" s="17" t="s">
@@ -4082,7 +4085,7 @@
       <c r="E81" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F81" s="36" t="s">
+      <c r="F81" s="35" t="s">
         <v>353</v>
       </c>
       <c r="J81" s="28" t="s">
@@ -4096,7 +4099,7 @@
       </c>
     </row>
     <row r="82" spans="3:12" x14ac:dyDescent="0.45">
-      <c r="C82" s="36" t="s">
+      <c r="C82" s="35" t="s">
         <v>241</v>
       </c>
       <c r="D82" s="17" t="s">
@@ -4105,7 +4108,7 @@
       <c r="E82" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F82" s="36" t="s">
+      <c r="F82" s="35" t="s">
         <v>354</v>
       </c>
       <c r="J82" s="28" t="s">
@@ -4119,7 +4122,7 @@
       </c>
     </row>
     <row r="83" spans="3:12" x14ac:dyDescent="0.45">
-      <c r="C83" s="36" t="s">
+      <c r="C83" s="35" t="s">
         <v>350</v>
       </c>
       <c r="D83" s="17" t="s">
@@ -4128,7 +4131,7 @@
       <c r="E83" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F83" s="36" t="s">
+      <c r="F83" s="35" t="s">
         <v>355</v>
       </c>
       <c r="J83" s="28" t="s">
@@ -4293,124 +4296,124 @@
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="44" t="s">
+      <c r="C6" s="41"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="45"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="43" t="s">
+      <c r="F6" s="41"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43" t="s">
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="43"/>
-      <c r="M6" s="43"/>
-      <c r="N6" s="43"/>
-      <c r="O6" s="43"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="46"/>
+      <c r="O6" s="46"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="42"/>
-      <c r="E7" s="40" t="s">
+      <c r="C7" s="44"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="41"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="40" t="s">
+      <c r="F7" s="44"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="41"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="40" t="s">
+      <c r="I7" s="44"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="41"/>
-      <c r="M7" s="41"/>
-      <c r="N7" s="41"/>
-      <c r="O7" s="42"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="45"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="40" t="s">
+      <c r="C8" s="44"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="41"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="40">
+      <c r="F8" s="44"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="43">
         <v>3</v>
       </c>
-      <c r="I8" s="41"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="40" t="s">
+      <c r="I8" s="44"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="41"/>
-      <c r="M8" s="41"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="42"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="45"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="40" t="s">
+      <c r="C9" s="44"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="41"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="40">
+      <c r="F9" s="44"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="43">
         <v>3</v>
       </c>
-      <c r="I9" s="41"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="40" t="s">
+      <c r="I9" s="44"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="42"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="45"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="40" t="s">
+      <c r="C10" s="44"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="40">
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="43">
         <v>3</v>
       </c>
-      <c r="I10" s="41"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="40" t="s">
+      <c r="I10" s="44"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="41"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="42"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="44"/>
+      <c r="O10" s="45"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B13" s="1" t="s">
@@ -4418,76 +4421,76 @@
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="44" t="s">
+      <c r="C14" s="41"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="45"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="43" t="s">
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43" t="s">
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="46"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="40" t="s">
+      <c r="C15" s="44"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="41"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="40" t="s">
+      <c r="F15" s="44"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="41"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="40" t="s">
+      <c r="I15" s="44"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="42"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="45"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="40" t="s">
+      <c r="C16" s="44"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="40" t="s">
+      <c r="F16" s="44"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="I16" s="41"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="40" t="s">
+      <c r="I16" s="44"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="42"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="45"/>
     </row>
     <row r="22" spans="3:24" x14ac:dyDescent="0.45">
       <c r="F22" s="4" t="s">
@@ -4518,11 +4521,11 @@
         <v>32</v>
       </c>
       <c r="N23" s="5"/>
-      <c r="P23" s="40" t="s">
+      <c r="P23" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="Q23" s="41"/>
-      <c r="R23" s="42"/>
+      <c r="Q23" s="44"/>
+      <c r="R23" s="45"/>
       <c r="S23" s="9" t="s">
         <v>73</v>
       </c>
@@ -4541,11 +4544,11 @@
         <v>75</v>
       </c>
       <c r="N24" s="5"/>
-      <c r="P24" s="40" t="s">
+      <c r="P24" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="Q24" s="41"/>
-      <c r="R24" s="42"/>
+      <c r="Q24" s="44"/>
+      <c r="R24" s="45"/>
       <c r="S24" s="8" t="s">
         <v>108</v>
       </c>
@@ -4567,11 +4570,11 @@
         <v>76</v>
       </c>
       <c r="N25" s="5"/>
-      <c r="P25" s="40" t="s">
+      <c r="P25" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="Q25" s="41"/>
-      <c r="R25" s="42"/>
+      <c r="Q25" s="44"/>
+      <c r="R25" s="45"/>
       <c r="S25" s="8" t="s">
         <v>111</v>
       </c>
@@ -4593,11 +4596,11 @@
         <v>77</v>
       </c>
       <c r="N26" s="5"/>
-      <c r="P26" s="40" t="s">
+      <c r="P26" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="Q26" s="41"/>
-      <c r="R26" s="42"/>
+      <c r="Q26" s="44"/>
+      <c r="R26" s="45"/>
       <c r="S26" s="8" t="s">
         <v>113</v>
       </c>
@@ -5547,6 +5550,28 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="P23:R23"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="P25:R25"/>
+    <mergeCell ref="P26:R26"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="K15:O15"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:O16"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:O14"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="K7:O7"/>
+    <mergeCell ref="K8:O8"/>
+    <mergeCell ref="K10:O10"/>
+    <mergeCell ref="K9:O9"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="B16:D16"/>
@@ -5561,28 +5586,6 @@
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="E14:G14"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="K14:O14"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="K7:O7"/>
-    <mergeCell ref="K8:O8"/>
-    <mergeCell ref="K10:O10"/>
-    <mergeCell ref="K9:O9"/>
-    <mergeCell ref="P23:R23"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="P25:R25"/>
-    <mergeCell ref="P26:R26"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="H15:J15"/>
-    <mergeCell ref="K15:O15"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="K16:O16"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/이벤트 스캐쥴.xlsx
+++ b/이벤트 스캐쥴.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fathermade\Desktop\스케쥴\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2278F629-0DD8-4C2F-B9BF-2040F4FB9744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11086FA1-AC6A-47E0-B811-AC8039FCE8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{960D76DD-7980-44EA-8846-33B5604DDBBF}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{960D76DD-7980-44EA-8846-33B5604DDBBF}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="399">
   <si>
     <t>※ 패키지 상품 판매 주기</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1410,6 +1410,36 @@
   </si>
   <si>
     <t>특별 보상!15</t>
+  </si>
+  <si>
+    <t>깜짝 보상!59</t>
+  </si>
+  <si>
+    <t>깜짝 보상!61</t>
+  </si>
+  <si>
+    <t>깜짝 보상!62</t>
+  </si>
+  <si>
+    <t>깜짝 보상!63</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>추석 보상!1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추석 보상!2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>깜짝 보상!60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1596,7 +1626,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1697,9 +1727,6 @@
     <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1708,9 +1735,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2070,7 +2094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{298AB57F-B69B-4CDE-AD7B-5D6372858410}">
-  <dimension ref="B2:T98"/>
+  <dimension ref="B2:T106"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="4" width="16.75" customWidth="1"/>
@@ -2137,10 +2161,10 @@
       <c r="F3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="35" t="s">
         <v>74</v>
       </c>
       <c r="J3" s="19" t="s">
@@ -2175,10 +2199,10 @@
       <c r="F4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>75</v>
       </c>
       <c r="J4" s="19" t="s">
@@ -2204,10 +2228,10 @@
       <c r="F5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="35" t="s">
         <v>76</v>
       </c>
       <c r="J5" s="19" t="s">
@@ -2233,10 +2257,10 @@
       <c r="F6" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="36" t="s">
+      <c r="G6" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="36" t="s">
+      <c r="H6" s="35" t="s">
         <v>77</v>
       </c>
       <c r="J6" s="19" t="s">
@@ -2577,7 +2601,7 @@
       <c r="H19" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="J19" s="35" t="s">
+      <c r="J19" s="34" t="s">
         <v>221</v>
       </c>
       <c r="K19" s="32" t="s">
@@ -2615,7 +2639,7 @@
       <c r="H20" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="J20" s="35" t="s">
+      <c r="J20" s="34" t="s">
         <v>222</v>
       </c>
       <c r="K20" s="32" t="s">
@@ -2653,7 +2677,7 @@
       <c r="H21" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="J21" s="35" t="s">
+      <c r="J21" s="34" t="s">
         <v>223</v>
       </c>
       <c r="K21" s="32" t="s">
@@ -2691,7 +2715,7 @@
       <c r="H22" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="J22" s="35" t="s">
+      <c r="J22" s="34" t="s">
         <v>224</v>
       </c>
       <c r="K22" s="32" t="s">
@@ -2755,7 +2779,7 @@
       <c r="H24" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="J24" s="35" t="s">
+      <c r="J24" s="34" t="s">
         <v>345</v>
       </c>
       <c r="K24" s="32" t="s">
@@ -2787,7 +2811,7 @@
       <c r="H25" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="J25" s="35" t="s">
+      <c r="J25" s="34" t="s">
         <v>362</v>
       </c>
       <c r="K25" s="32" t="s">
@@ -2819,7 +2843,7 @@
       <c r="H26" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="J26" s="35" t="s">
+      <c r="J26" s="34" t="s">
         <v>365</v>
       </c>
       <c r="K26" s="32" t="s">
@@ -2845,7 +2869,7 @@
       <c r="H27" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="J27" s="35"/>
+      <c r="J27" s="34"/>
       <c r="K27" s="32"/>
       <c r="L27" s="32"/>
       <c r="N27" s="19"/>
@@ -2865,7 +2889,7 @@
       <c r="H28" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="J28" s="35"/>
+      <c r="J28" s="34"/>
       <c r="K28" s="32"/>
       <c r="L28" s="32"/>
       <c r="N28" s="19"/>
@@ -2885,7 +2909,7 @@
       <c r="H29" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="J29" s="35"/>
+      <c r="J29" s="34"/>
       <c r="K29" s="32"/>
       <c r="L29" s="32"/>
       <c r="N29" s="19"/>
@@ -2905,7 +2929,7 @@
       <c r="H30" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="J30" s="35"/>
+      <c r="J30" s="34"/>
       <c r="K30" s="32"/>
       <c r="L30" s="32"/>
       <c r="N30" s="19"/>
@@ -2925,7 +2949,7 @@
       <c r="H31" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="J31" s="35"/>
+      <c r="J31" s="34"/>
       <c r="K31" s="32"/>
       <c r="L31" s="32"/>
       <c r="N31" s="19"/>
@@ -2953,7 +2977,7 @@
       <c r="T32" s="21"/>
     </row>
     <row r="33" spans="6:20" x14ac:dyDescent="0.45">
-      <c r="F33" s="35" t="s">
+      <c r="F33" s="34" t="s">
         <v>60</v>
       </c>
       <c r="G33" s="17" t="s">
@@ -2979,7 +3003,7 @@
       <c r="T33" s="21"/>
     </row>
     <row r="34" spans="6:20" x14ac:dyDescent="0.45">
-      <c r="F34" s="35" t="s">
+      <c r="F34" s="34" t="s">
         <v>61</v>
       </c>
       <c r="G34" s="17" t="s">
@@ -3005,7 +3029,7 @@
       <c r="T34" s="21"/>
     </row>
     <row r="35" spans="6:20" x14ac:dyDescent="0.45">
-      <c r="F35" s="35" t="s">
+      <c r="F35" s="34" t="s">
         <v>62</v>
       </c>
       <c r="G35" s="17" t="s">
@@ -3378,10 +3402,10 @@
       <c r="N49" s="28" t="s">
         <v>379</v>
       </c>
-      <c r="O49" s="34" t="s">
+      <c r="O49" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="P49" s="34" t="s">
+      <c r="P49" s="30" t="s">
         <v>227</v>
       </c>
     </row>
@@ -3407,15 +3431,15 @@
       <c r="N50" s="28" t="s">
         <v>380</v>
       </c>
-      <c r="O50" s="34" t="s">
+      <c r="O50" s="30" t="s">
         <v>333</v>
       </c>
-      <c r="P50" s="34" t="s">
+      <c r="P50" s="30" t="s">
         <v>333</v>
       </c>
-      <c r="Q50" s="39"/>
-      <c r="R50" s="39"/>
-      <c r="S50" s="39"/>
+      <c r="Q50" s="37"/>
+      <c r="R50" s="37"/>
+      <c r="S50" s="37"/>
     </row>
     <row r="51" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F51" s="16" t="s">
@@ -3439,15 +3463,15 @@
       <c r="N51" s="28" t="s">
         <v>383</v>
       </c>
-      <c r="O51" s="34" t="s">
+      <c r="O51" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="P51" s="34" t="s">
+      <c r="P51" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="Q51" s="39"/>
-      <c r="R51" s="39"/>
-      <c r="S51" s="39"/>
+      <c r="Q51" s="37"/>
+      <c r="R51" s="37"/>
+      <c r="S51" s="37"/>
     </row>
     <row r="52" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F52" s="16" t="s">
@@ -3471,15 +3495,15 @@
       <c r="N52" s="28" t="s">
         <v>384</v>
       </c>
-      <c r="O52" s="34" t="s">
+      <c r="O52" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="P52" s="34" t="s">
+      <c r="P52" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="Q52" s="39"/>
-      <c r="R52" s="39"/>
-      <c r="S52" s="39"/>
+      <c r="Q52" s="37"/>
+      <c r="R52" s="37"/>
+      <c r="S52" s="37"/>
     </row>
     <row r="53" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F53" s="16" t="s">
@@ -3503,15 +3527,15 @@
       <c r="N53" s="28" t="s">
         <v>385</v>
       </c>
-      <c r="O53" s="34" t="s">
+      <c r="O53" s="30" t="s">
         <v>381</v>
       </c>
-      <c r="P53" s="34" t="s">
+      <c r="P53" s="30" t="s">
         <v>381</v>
       </c>
-      <c r="Q53" s="39"/>
-      <c r="R53" s="39"/>
-      <c r="S53" s="39"/>
+      <c r="Q53" s="37"/>
+      <c r="R53" s="37"/>
+      <c r="S53" s="37"/>
     </row>
     <row r="54" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F54" s="16" t="s">
@@ -3535,15 +3559,15 @@
       <c r="N54" s="28" t="s">
         <v>386</v>
       </c>
-      <c r="O54" s="34" t="s">
+      <c r="O54" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="P54" s="34" t="s">
+      <c r="P54" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="Q54" s="39"/>
-      <c r="R54" s="39"/>
-      <c r="S54" s="39"/>
+      <c r="Q54" s="37"/>
+      <c r="R54" s="37"/>
+      <c r="S54" s="37"/>
     </row>
     <row r="55" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F55" s="16" t="s">
@@ -3567,15 +3591,15 @@
       <c r="N55" s="28" t="s">
         <v>387</v>
       </c>
-      <c r="O55" s="38" t="s">
+      <c r="O55" s="33" t="s">
         <v>342</v>
       </c>
-      <c r="P55" s="38" t="s">
+      <c r="P55" s="33" t="s">
         <v>342</v>
       </c>
-      <c r="Q55" s="39"/>
-      <c r="R55" s="39"/>
-      <c r="S55" s="39"/>
+      <c r="Q55" s="37"/>
+      <c r="R55" s="37"/>
+      <c r="S55" s="37"/>
     </row>
     <row r="56" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F56" s="16" t="s">
@@ -3599,15 +3623,15 @@
       <c r="N56" s="28" t="s">
         <v>388</v>
       </c>
-      <c r="O56" s="38" t="s">
+      <c r="O56" s="33" t="s">
         <v>346</v>
       </c>
-      <c r="P56" s="38" t="s">
+      <c r="P56" s="33" t="s">
         <v>346</v>
       </c>
-      <c r="Q56" s="39"/>
-      <c r="R56" s="39"/>
-      <c r="S56" s="39"/>
+      <c r="Q56" s="37"/>
+      <c r="R56" s="37"/>
+      <c r="S56" s="37"/>
     </row>
     <row r="57" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F57" s="16" t="s">
@@ -3631,15 +3655,15 @@
       <c r="N57" s="28" t="s">
         <v>389</v>
       </c>
-      <c r="O57" s="38" t="s">
+      <c r="O57" s="33" t="s">
         <v>363</v>
       </c>
-      <c r="P57" s="38" t="s">
+      <c r="P57" s="33" t="s">
         <v>363</v>
       </c>
-      <c r="Q57" s="39"/>
-      <c r="R57" s="39"/>
-      <c r="S57" s="39"/>
+      <c r="Q57" s="37"/>
+      <c r="R57" s="37"/>
+      <c r="S57" s="37"/>
     </row>
     <row r="58" spans="4:19" x14ac:dyDescent="0.45">
       <c r="F58" s="16" t="s">
@@ -3837,7 +3861,7 @@
       <c r="L68" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="R68" s="37" t="s">
+      <c r="R68" s="36" t="s">
         <v>63</v>
       </c>
       <c r="S68" s="31" t="s">
@@ -3857,7 +3881,7 @@
       <c r="L69" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="R69" s="37" t="s">
+      <c r="R69" s="36" t="s">
         <v>64</v>
       </c>
       <c r="S69" s="31" t="s">
@@ -3877,7 +3901,7 @@
       <c r="L70" s="30" t="s">
         <v>280</v>
       </c>
-      <c r="R70" s="37" t="s">
+      <c r="R70" s="36" t="s">
         <v>65</v>
       </c>
       <c r="S70" s="31" t="s">
@@ -3897,7 +3921,7 @@
       <c r="L71" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="R71" s="37" t="s">
+      <c r="R71" s="36" t="s">
         <v>66</v>
       </c>
       <c r="S71" s="31" t="s">
@@ -3917,7 +3941,7 @@
       <c r="L72" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="R72" s="37" t="s">
+      <c r="R72" s="36" t="s">
         <v>67</v>
       </c>
       <c r="S72" s="31" t="s">
@@ -3937,7 +3961,7 @@
       <c r="L73" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="R73" s="37" t="s">
+      <c r="R73" s="36" t="s">
         <v>68</v>
       </c>
       <c r="S73" s="31" t="s">
@@ -3957,7 +3981,7 @@
       <c r="L74" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="R74" s="37" t="s">
+      <c r="R74" s="36" t="s">
         <v>69</v>
       </c>
       <c r="S74" s="31" t="s">
@@ -3977,7 +4001,7 @@
       <c r="L75" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="R75" s="37" t="s">
+      <c r="R75" s="36" t="s">
         <v>70</v>
       </c>
       <c r="S75" s="31" t="s">
@@ -3997,7 +4021,7 @@
       <c r="L76" s="30" t="s">
         <v>199</v>
       </c>
-      <c r="R76" s="37" t="s">
+      <c r="R76" s="36" t="s">
         <v>71</v>
       </c>
       <c r="S76" s="31" t="s">
@@ -4053,7 +4077,7 @@
       </c>
     </row>
     <row r="80" spans="3:20" x14ac:dyDescent="0.45">
-      <c r="C80" s="35" t="s">
+      <c r="C80" s="34" t="s">
         <v>239</v>
       </c>
       <c r="D80" s="17" t="s">
@@ -4062,7 +4086,7 @@
       <c r="E80" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F80" s="35" t="s">
+      <c r="F80" s="34" t="s">
         <v>351</v>
       </c>
       <c r="J80" s="28" t="s">
@@ -4076,7 +4100,7 @@
       </c>
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.45">
-      <c r="C81" s="35" t="s">
+      <c r="C81" s="34" t="s">
         <v>240</v>
       </c>
       <c r="D81" s="17" t="s">
@@ -4085,7 +4109,7 @@
       <c r="E81" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F81" s="35" t="s">
+      <c r="F81" s="34" t="s">
         <v>353</v>
       </c>
       <c r="J81" s="28" t="s">
@@ -4099,7 +4123,7 @@
       </c>
     </row>
     <row r="82" spans="3:12" x14ac:dyDescent="0.45">
-      <c r="C82" s="35" t="s">
+      <c r="C82" s="34" t="s">
         <v>241</v>
       </c>
       <c r="D82" s="17" t="s">
@@ -4108,7 +4132,7 @@
       <c r="E82" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F82" s="35" t="s">
+      <c r="F82" s="34" t="s">
         <v>354</v>
       </c>
       <c r="J82" s="28" t="s">
@@ -4122,7 +4146,7 @@
       </c>
     </row>
     <row r="83" spans="3:12" x14ac:dyDescent="0.45">
-      <c r="C83" s="35" t="s">
+      <c r="C83" s="34" t="s">
         <v>350</v>
       </c>
       <c r="D83" s="17" t="s">
@@ -4131,7 +4155,7 @@
       <c r="E83" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="F83" s="35" t="s">
+      <c r="F83" s="34" t="s">
         <v>355</v>
       </c>
       <c r="J83" s="28" t="s">
@@ -4233,39 +4257,121 @@
       </c>
     </row>
     <row r="92" spans="3:12" x14ac:dyDescent="0.45">
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
-      <c r="L92" s="2"/>
+      <c r="J92" s="28" t="s">
+        <v>390</v>
+      </c>
+      <c r="K92" s="30" t="s">
+        <v>394</v>
+      </c>
+      <c r="L92" s="30" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="93" spans="3:12" x14ac:dyDescent="0.45">
-      <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
-      <c r="L93" s="2"/>
+      <c r="J93" s="28" t="s">
+        <v>396</v>
+      </c>
+      <c r="K93" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="L93" s="30" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="94" spans="3:12" x14ac:dyDescent="0.45">
-      <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
-      <c r="L94" s="2"/>
+      <c r="J94" s="28" t="s">
+        <v>397</v>
+      </c>
+      <c r="K94" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="L94" s="30" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="95" spans="3:12" x14ac:dyDescent="0.45">
-      <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
-      <c r="L95" s="2"/>
+      <c r="J95" s="28" t="s">
+        <v>398</v>
+      </c>
+      <c r="K95" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="L95" s="30" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="96" spans="3:12" x14ac:dyDescent="0.45">
-      <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
-      <c r="L96" s="2"/>
+      <c r="J96" s="28" t="s">
+        <v>391</v>
+      </c>
+      <c r="K96" s="30" t="s">
+        <v>336</v>
+      </c>
+      <c r="L96" s="30" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="97" spans="10:12" x14ac:dyDescent="0.45">
-      <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
-      <c r="L97" s="2"/>
+      <c r="J97" s="28" t="s">
+        <v>392</v>
+      </c>
+      <c r="K97" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="L97" s="30" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="98" spans="10:12" x14ac:dyDescent="0.45">
-      <c r="J98" s="2"/>
-      <c r="K98" s="2"/>
-      <c r="L98" s="2"/>
+      <c r="J98" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="K98" s="30" t="s">
+        <v>395</v>
+      </c>
+      <c r="L98" s="30" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="99" spans="10:12" x14ac:dyDescent="0.45">
+      <c r="J99" s="2"/>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
+    </row>
+    <row r="100" spans="10:12" x14ac:dyDescent="0.45">
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
+    </row>
+    <row r="101" spans="10:12" x14ac:dyDescent="0.45">
+      <c r="J101" s="2"/>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
+    </row>
+    <row r="102" spans="10:12" x14ac:dyDescent="0.45">
+      <c r="J102" s="2"/>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
+    </row>
+    <row r="103" spans="10:12" x14ac:dyDescent="0.45">
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
+    </row>
+    <row r="104" spans="10:12" x14ac:dyDescent="0.45">
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
+    </row>
+    <row r="105" spans="10:12" x14ac:dyDescent="0.45">
+      <c r="J105" s="2"/>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
+    </row>
+    <row r="106" spans="10:12" x14ac:dyDescent="0.45">
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4296,124 +4402,124 @@
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="40" t="s">
+      <c r="C6" s="39"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="41"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="46" t="s">
+      <c r="F6" s="39"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46" t="s">
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="46"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="43" t="s">
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="43" t="s">
+      <c r="F7" s="42"/>
+      <c r="G7" s="43"/>
+      <c r="H7" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="44"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="43" t="s">
+      <c r="I7" s="42"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="45"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="43"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="44"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="43" t="s">
+      <c r="C8" s="42"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="44"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="43">
+      <c r="F8" s="42"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="41">
         <v>3</v>
       </c>
-      <c r="I8" s="44"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="43" t="s">
+      <c r="I8" s="42"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="45"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="42"/>
+      <c r="O8" s="43"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="44"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="43" t="s">
+      <c r="C9" s="42"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="44"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="43">
+      <c r="F9" s="42"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="41">
         <v>3</v>
       </c>
-      <c r="I9" s="44"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="43" t="s">
+      <c r="I9" s="42"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="45"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="42"/>
+      <c r="O9" s="43"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="44"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="43" t="s">
+      <c r="C10" s="42"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="44"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="43">
+      <c r="F10" s="42"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="41">
         <v>3</v>
       </c>
-      <c r="I10" s="44"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="43" t="s">
+      <c r="I10" s="42"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="45"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="43"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B13" s="1" t="s">
@@ -4421,76 +4527,76 @@
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="40" t="s">
+      <c r="C14" s="39"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="41"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="46" t="s">
+      <c r="F14" s="39"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46" t="s">
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="46"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="44"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="43" t="s">
+      <c r="C15" s="42"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="44"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="43" t="s">
+      <c r="F15" s="42"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="44"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="43" t="s">
+      <c r="I15" s="42"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="L15" s="44"/>
-      <c r="M15" s="44"/>
-      <c r="N15" s="44"/>
-      <c r="O15" s="45"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="43"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="43" t="s">
+      <c r="C16" s="42"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="44"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="43" t="s">
+      <c r="F16" s="42"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="I16" s="44"/>
-      <c r="J16" s="45"/>
-      <c r="K16" s="43" t="s">
+      <c r="I16" s="42"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="44"/>
-      <c r="M16" s="44"/>
-      <c r="N16" s="44"/>
-      <c r="O16" s="45"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="43"/>
     </row>
     <row r="22" spans="3:24" x14ac:dyDescent="0.45">
       <c r="F22" s="4" t="s">
@@ -4521,11 +4627,11 @@
         <v>32</v>
       </c>
       <c r="N23" s="5"/>
-      <c r="P23" s="43" t="s">
+      <c r="P23" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="Q23" s="44"/>
-      <c r="R23" s="45"/>
+      <c r="Q23" s="42"/>
+      <c r="R23" s="43"/>
       <c r="S23" s="9" t="s">
         <v>73</v>
       </c>
@@ -4544,11 +4650,11 @@
         <v>75</v>
       </c>
       <c r="N24" s="5"/>
-      <c r="P24" s="43" t="s">
+      <c r="P24" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="Q24" s="44"/>
-      <c r="R24" s="45"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="43"/>
       <c r="S24" s="8" t="s">
         <v>108</v>
       </c>
@@ -4570,11 +4676,11 @@
         <v>76</v>
       </c>
       <c r="N25" s="5"/>
-      <c r="P25" s="43" t="s">
+      <c r="P25" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="Q25" s="44"/>
-      <c r="R25" s="45"/>
+      <c r="Q25" s="42"/>
+      <c r="R25" s="43"/>
       <c r="S25" s="8" t="s">
         <v>111</v>
       </c>
@@ -4596,11 +4702,11 @@
         <v>77</v>
       </c>
       <c r="N26" s="5"/>
-      <c r="P26" s="43" t="s">
+      <c r="P26" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="Q26" s="44"/>
-      <c r="R26" s="45"/>
+      <c r="Q26" s="42"/>
+      <c r="R26" s="43"/>
       <c r="S26" s="8" t="s">
         <v>113</v>
       </c>
